--- a/backend/src/evolve/Kelsic_Data_foldy/Round_7_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_7_top_variants.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,121 +443,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E56W</t>
+          <t>L17T</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.955</v>
+        <v>0.97525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E56F</t>
+          <t>K52W</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9395</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E56L</t>
+          <t>H30Y</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9598333333333332</v>
+        <v>0.9864999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E56T</t>
+          <t>H30L</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.96975</v>
+        <v>0.9848333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E56V</t>
+          <t>P59F</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9794999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E56Y</t>
+          <t>P59N</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9715</v>
+        <v>0.9430000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S71V</t>
+          <t>T12W</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.99075</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N19T</t>
+          <t>N19P</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.00275</v>
+        <v>0.70075</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E56Q</t>
+          <t>L17W</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9915</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T49Y</t>
+          <t>P59W</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.907</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S71W</t>
+          <t>H30V</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.012</v>
+        <v>1.00475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E56A</t>
+          <t>P59H</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.987</v>
+        <v>0.9315</v>
       </c>
     </row>
     <row r="14">
@@ -573,71 +573,71 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N43A</t>
+          <t>I67L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9082500000000001</v>
+        <v>0.9594999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H35I</t>
+          <t>Q10A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9873333333333333</v>
+        <v>0.7132499999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V68L</t>
+          <t>P59A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9823333333333334</v>
+        <v>0.9742500000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V68R</t>
+          <t>H30T</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.984</v>
+        <v>0.9844999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N6Y</t>
+          <t>S71I</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.005</v>
+        <v>0.9783333333333334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T54K</t>
+          <t>T12R</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9339999999999999</v>
+        <v>0.9778333333333333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T54R</t>
+          <t>P59Q</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9778333333333333</v>
+        <v>0.971</v>
       </c>
     </row>
   </sheetData>
